--- a/Projects/History catchup and code/cogm_history.xlsx
+++ b/Projects/History catchup and code/cogm_history.xlsx
@@ -1,16 +1,16 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
-  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="10821"/>
+  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="11004"/>
   <workbookPr defaultThemeVersion="202300"/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="/Users/Seth/Desktop/github_repos/SHL/Projects/History catchup and code/"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{FB4E3813-2B43-A941-9EC5-983B84A02EB9}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{B8AD4A0D-32ED-FC47-A0A5-EB99C8C8968E}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="14460" yWindow="660" windowWidth="14180" windowHeight="16060" xr2:uid="{034BB17B-769C-7C48-8890-9568CD0B4131}"/>
+    <workbookView xWindow="140" yWindow="660" windowWidth="15480" windowHeight="16060" activeTab="1" xr2:uid="{034BB17B-769C-7C48-8890-9568CD0B4131}"/>
   </bookViews>
   <sheets>
     <sheet name="shl" sheetId="1" r:id="rId1"/>
@@ -40,7 +40,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="88" uniqueCount="85">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="88" uniqueCount="82">
   <si>
     <t>gm</t>
   </si>
@@ -207,9 +207,6 @@
     <t>caleb</t>
   </si>
   <si>
-    <t>jr95</t>
-  </si>
-  <si>
     <t>mattebleu</t>
   </si>
   <si>
@@ -228,9 +225,6 @@
     <t>kalesalad</t>
   </si>
   <si>
-    <t>jreiser</t>
-  </si>
-  <si>
     <t>oats</t>
   </si>
   <si>
@@ -252,18 +246,12 @@
     <t>ghamms</t>
   </si>
   <si>
-    <t>belmont</t>
-  </si>
-  <si>
     <t>zerg</t>
   </si>
   <si>
     <t>sg_vesuvius</t>
   </si>
   <si>
-    <t>sobrien</t>
-  </si>
-  <si>
     <t>NULL</t>
   </si>
   <si>
@@ -273,9 +261,6 @@
     <t>chareth</t>
   </si>
   <si>
-    <t>babufrik</t>
-  </si>
-  <si>
     <t>hacob</t>
   </si>
   <si>
@@ -295,6 +280,12 @@
   </si>
   <si>
     <t>nasbase</t>
+  </si>
+  <si>
+    <t>synes7hesia</t>
+  </si>
+  <si>
+    <t>denia11</t>
   </si>
 </sst>
 </file>
@@ -754,7 +745,7 @@
     </row>
     <row r="7" spans="1:4" x14ac:dyDescent="0.2">
       <c r="A7" s="1" t="s">
-        <v>84</v>
+        <v>79</v>
       </c>
       <c r="B7" s="1" t="s">
         <v>9</v>
@@ -830,7 +821,7 @@
     </row>
     <row r="13" spans="1:4" x14ac:dyDescent="0.2">
       <c r="A13" s="1" t="s">
-        <v>55</v>
+        <v>70</v>
       </c>
       <c r="B13" s="1" t="s">
         <v>15</v>
@@ -842,7 +833,7 @@
     </row>
     <row r="14" spans="1:4" x14ac:dyDescent="0.2">
       <c r="A14" s="1" t="s">
-        <v>56</v>
+        <v>55</v>
       </c>
       <c r="B14" s="1" t="s">
         <v>16</v>
@@ -854,7 +845,7 @@
     </row>
     <row r="15" spans="1:4" x14ac:dyDescent="0.2">
       <c r="A15" s="1" t="s">
-        <v>57</v>
+        <v>56</v>
       </c>
       <c r="B15" s="1" t="s">
         <v>17</v>
@@ -866,7 +857,7 @@
     </row>
     <row r="16" spans="1:4" x14ac:dyDescent="0.2">
       <c r="A16" s="1" t="s">
-        <v>58</v>
+        <v>57</v>
       </c>
       <c r="B16" s="1" t="s">
         <v>18</v>
@@ -878,7 +869,7 @@
     </row>
     <row r="17" spans="1:4" x14ac:dyDescent="0.2">
       <c r="A17" s="1" t="s">
-        <v>59</v>
+        <v>58</v>
       </c>
       <c r="B17" s="1" t="s">
         <v>19</v>
@@ -890,7 +881,7 @@
     </row>
     <row r="18" spans="1:4" x14ac:dyDescent="0.2">
       <c r="A18" s="1" t="s">
-        <v>60</v>
+        <v>59</v>
       </c>
       <c r="B18" s="1" t="s">
         <v>20</v>
@@ -902,7 +893,7 @@
     </row>
     <row r="19" spans="1:4" x14ac:dyDescent="0.2">
       <c r="A19" s="1" t="s">
-        <v>61</v>
+        <v>60</v>
       </c>
       <c r="B19" s="1" t="s">
         <v>21</v>
@@ -914,7 +905,7 @@
     </row>
     <row r="20" spans="1:4" x14ac:dyDescent="0.2">
       <c r="A20" s="1" t="s">
-        <v>62</v>
+        <v>80</v>
       </c>
       <c r="B20" s="1" t="s">
         <v>22</v>
@@ -926,7 +917,7 @@
     </row>
     <row r="21" spans="1:4" x14ac:dyDescent="0.2">
       <c r="A21" s="1" t="s">
-        <v>63</v>
+        <v>61</v>
       </c>
       <c r="B21" s="1" t="s">
         <v>23</v>
@@ -938,7 +929,7 @@
     </row>
     <row r="22" spans="1:4" x14ac:dyDescent="0.2">
       <c r="A22" s="1" t="s">
-        <v>64</v>
+        <v>62</v>
       </c>
       <c r="B22" s="1" t="s">
         <v>24</v>
@@ -950,7 +941,7 @@
     </row>
     <row r="23" spans="1:4" x14ac:dyDescent="0.2">
       <c r="A23" s="1" t="s">
-        <v>65</v>
+        <v>63</v>
       </c>
       <c r="B23" s="1" t="s">
         <v>25</v>
@@ -962,7 +953,7 @@
     </row>
     <row r="24" spans="1:4" x14ac:dyDescent="0.2">
       <c r="A24" s="1" t="s">
-        <v>66</v>
+        <v>64</v>
       </c>
       <c r="B24" s="1" t="s">
         <v>26</v>
@@ -974,7 +965,7 @@
     </row>
     <row r="25" spans="1:4" x14ac:dyDescent="0.2">
       <c r="A25" s="1" t="s">
-        <v>67</v>
+        <v>65</v>
       </c>
       <c r="B25" s="1" t="s">
         <v>27</v>
@@ -1010,7 +1001,7 @@
     </row>
     <row r="2" spans="1:4" x14ac:dyDescent="0.2">
       <c r="A2" s="1" t="s">
-        <v>68</v>
+        <v>66</v>
       </c>
       <c r="B2" s="1" t="s">
         <v>29</v>
@@ -1022,7 +1013,7 @@
     </row>
     <row r="3" spans="1:4" x14ac:dyDescent="0.2">
       <c r="A3" s="1" t="s">
-        <v>69</v>
+        <v>67</v>
       </c>
       <c r="B3" s="1" t="s">
         <v>30</v>
@@ -1046,7 +1037,7 @@
     </row>
     <row r="5" spans="1:4" x14ac:dyDescent="0.2">
       <c r="A5" s="1" t="s">
-        <v>71</v>
+        <v>68</v>
       </c>
       <c r="B5" s="1" t="s">
         <v>32</v>
@@ -1058,7 +1049,7 @@
     </row>
     <row r="6" spans="1:4" x14ac:dyDescent="0.2">
       <c r="A6" s="1" t="s">
-        <v>72</v>
+        <v>69</v>
       </c>
       <c r="B6" s="1" t="s">
         <v>33</v>
@@ -1070,7 +1061,7 @@
     </row>
     <row r="7" spans="1:4" x14ac:dyDescent="0.2">
       <c r="A7" s="1" t="s">
-        <v>73</v>
+        <v>81</v>
       </c>
       <c r="B7" s="1" t="s">
         <v>34</v>
@@ -1082,7 +1073,7 @@
     </row>
     <row r="8" spans="1:4" x14ac:dyDescent="0.2">
       <c r="A8" s="1" t="s">
-        <v>74</v>
+        <v>70</v>
       </c>
       <c r="B8" s="1" t="s">
         <v>35</v>
@@ -1094,7 +1085,7 @@
     </row>
     <row r="9" spans="1:4" x14ac:dyDescent="0.2">
       <c r="A9" s="1" t="s">
-        <v>75</v>
+        <v>71</v>
       </c>
       <c r="B9" s="1" t="s">
         <v>36</v>
@@ -1106,7 +1097,7 @@
     </row>
     <row r="10" spans="1:4" x14ac:dyDescent="0.2">
       <c r="A10" s="1" t="s">
-        <v>76</v>
+        <v>72</v>
       </c>
       <c r="B10" s="1" t="s">
         <v>37</v>
@@ -1118,7 +1109,7 @@
     </row>
     <row r="11" spans="1:4" x14ac:dyDescent="0.2">
       <c r="A11" s="1" t="s">
-        <v>77</v>
+        <v>70</v>
       </c>
       <c r="B11" s="1" t="s">
         <v>38</v>
@@ -1130,7 +1121,7 @@
     </row>
     <row r="12" spans="1:4" x14ac:dyDescent="0.2">
       <c r="A12" s="1" t="s">
-        <v>78</v>
+        <v>73</v>
       </c>
       <c r="B12" s="1" t="s">
         <v>39</v>
@@ -1142,7 +1133,7 @@
     </row>
     <row r="13" spans="1:4" x14ac:dyDescent="0.2">
       <c r="A13" s="1" t="s">
-        <v>79</v>
+        <v>74</v>
       </c>
       <c r="B13" s="1" t="s">
         <v>40</v>
@@ -1154,7 +1145,7 @@
     </row>
     <row r="14" spans="1:4" x14ac:dyDescent="0.2">
       <c r="A14" s="1" t="s">
-        <v>80</v>
+        <v>75</v>
       </c>
       <c r="B14" s="1" t="s">
         <v>41</v>
@@ -1166,7 +1157,7 @@
     </row>
     <row r="15" spans="1:4" x14ac:dyDescent="0.2">
       <c r="A15" s="1" t="s">
-        <v>81</v>
+        <v>76</v>
       </c>
       <c r="B15" s="1" t="s">
         <v>42</v>
@@ -1178,7 +1169,7 @@
     </row>
     <row r="16" spans="1:4" x14ac:dyDescent="0.2">
       <c r="A16" s="1" t="s">
-        <v>82</v>
+        <v>77</v>
       </c>
       <c r="B16" s="1" t="s">
         <v>43</v>
@@ -1190,7 +1181,7 @@
     </row>
     <row r="17" spans="1:4" x14ac:dyDescent="0.2">
       <c r="A17" s="1" t="s">
-        <v>83</v>
+        <v>78</v>
       </c>
       <c r="B17" s="1" t="s">
         <v>44</v>
